--- a/PythonTesting/reports/Failed_Test_Cases.xlsx
+++ b/PythonTesting/reports/Failed_Test_Cases.xlsx
@@ -2500,7 +2500,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1555ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1947ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1933ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1688ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1645ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1790ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1739ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1756ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1794ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1939ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1713ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1706ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1922ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1784ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1631ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1621ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1766ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1874ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1725ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1901ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1944ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1785ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1705ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1933ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1669ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1749ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1803ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1667ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1789ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1821ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1561ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1859ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1586ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1939ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>

--- a/PythonTesting/reports/Failed_Test_Cases.xlsx
+++ b/PythonTesting/reports/Failed_Test_Cases.xlsx
@@ -2500,7 +2500,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1947ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1705ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1688ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1934ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1790ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1879ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1756ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1777ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1939ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1782ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1706ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1707ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1784ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1743ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1621ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1861ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1874ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1773ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1901ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1890ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1785ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1686ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1933ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1582ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1749ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1712ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1667ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1928ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1821ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1902ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1859ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1835ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Latency SLA Violation: P95 Response latency of 1939ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
+          <t>Latency SLA Violation: P95 Response latency of 1783ms exceeded target threshold of 1500ms under 100 VU concurrent load.</t>
         </is>
       </c>
     </row>
